--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-related-person.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="163">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>Lien avec le patient</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-hl7-v3-PersonalRelationshipRoleType-cisis</t>
@@ -1432,13 +1435,13 @@
         <v>73</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
@@ -1473,10 +1476,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1499,13 +1502,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1556,7 +1559,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1573,10 +1576,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1599,13 +1602,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1656,7 +1659,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1673,10 +1676,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1702,10 +1705,10 @@
         <v>89</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1732,13 +1735,13 @@
         <v>73</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>73</v>
@@ -1756,7 +1759,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1773,10 +1776,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1799,13 +1802,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1856,7 +1859,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1873,10 +1876,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1899,13 +1902,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1956,7 +1959,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1968,15 +1971,15 @@
         <v>73</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1999,13 +2002,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2056,7 +2059,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2073,14 +2076,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2099,16 +2102,16 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2146,19 +2149,19 @@
         <v>73</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2170,19 +2173,19 @@
         <v>73</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2195,25 +2198,25 @@
         <v>73</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>73</v>
@@ -2262,7 +2265,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2274,15 +2277,15 @@
         <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2305,13 +2308,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2362,7 +2365,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2379,10 +2382,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2405,13 +2408,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2462,7 +2465,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>74</v>
@@ -2479,10 +2482,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2505,13 +2508,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2562,7 +2565,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2574,15 +2577,15 @@
         <v>73</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2605,13 +2608,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2662,7 +2665,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2679,14 +2682,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -2705,16 +2708,16 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2752,19 +2755,19 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2776,19 +2779,19 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -2801,25 +2804,25 @@
         <v>73</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>73</v>
@@ -2868,7 +2871,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2880,15 +2883,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2911,13 +2914,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2968,7 +2971,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2985,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3011,13 +3014,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3068,7 +3071,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3085,10 +3088,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3111,13 +3114,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3168,7 +3171,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3185,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3211,13 +3214,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3268,7 +3271,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3285,10 +3288,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3311,13 +3314,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3368,7 +3371,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3380,15 +3383,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3411,13 +3414,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3468,7 +3471,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3485,14 +3488,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3511,16 +3514,16 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3558,19 +3561,19 @@
         <v>73</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3582,19 +3585,19 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -3607,25 +3610,25 @@
         <v>73</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>73</v>
@@ -3674,7 +3677,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3686,15 +3689,15 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3720,10 +3723,10 @@
         <v>89</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3774,7 +3777,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>85</v>
@@ -3791,10 +3794,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3817,13 +3820,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3874,7 +3877,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
